--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N59_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N59_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.61019886989339</v>
+        <v>5.949157316357676</v>
       </c>
       <c r="D2" t="n">
-        <v>36.93234155874384</v>
+        <v>6.001505503295875</v>
       </c>
       <c r="E2" t="n">
-        <v>3.543217527715736</v>
+        <v>0.575772848253807</v>
       </c>
       <c r="F2" t="n">
-        <v>3.550940790780134</v>
+        <v>0.5770278785017715</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.69403420507015</v>
+        <v>5.312780558323899</v>
       </c>
       <c r="D3" t="n">
-        <v>33.22042063436789</v>
+        <v>5.398318353084782</v>
       </c>
       <c r="E3" t="n">
-        <v>3.543217527715736</v>
+        <v>0.575772848253807</v>
       </c>
       <c r="F3" t="n">
-        <v>3.550940790780134</v>
+        <v>0.5770278785017715</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.35976126254707</v>
+        <v>6.7209612051639</v>
       </c>
       <c r="D4" t="n">
-        <v>41.88868940847944</v>
+        <v>6.806912028877909</v>
       </c>
       <c r="E4" t="n">
-        <v>3.543217527715736</v>
+        <v>0.575772848253807</v>
       </c>
       <c r="F4" t="n">
-        <v>3.550940790780134</v>
+        <v>0.5770278785017715</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
